--- a/hwk4/test_data.xlsx
+++ b/hwk4/test_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10123"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robinburke/Dropbox/2019_aSpring/INFO4871/hwk/hwk4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yushuo Ruan\Dropbox\Spring2019\RecommenderSystems\Gitrepo\hwk4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA045D89-11CE-F647-939F-9719081CEDE6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2ED80F-AAD7-434B-A0B0-CBB1835CE44A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10940" yWindow="2440" windowWidth="21180" windowHeight="16420" activeTab="4" xr2:uid="{D8D605F8-015C-0740-BF92-A813C61E88C3}"/>
+    <workbookView xWindow="10935" yWindow="2445" windowWidth="21180" windowHeight="16425" firstSheet="2" activeTab="4" xr2:uid="{D8D605F8-015C-0740-BF92-A813C61E88C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Rating Data" sheetId="1" r:id="rId1"/>
@@ -151,7 +151,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -174,6 +174,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF7E00"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -222,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -233,6 +239,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -548,9 +555,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070273A3-5EC5-9C43-9450-2903119A867A}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -572,7 +579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -583,7 +590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -594,7 +601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -605,7 +612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -616,7 +623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -627,7 +634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -638,7 +645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
@@ -649,7 +656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
@@ -660,7 +667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
@@ -671,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -682,7 +689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
@@ -693,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4</v>
       </c>
@@ -704,7 +711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
@@ -715,7 +722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>5</v>
       </c>
@@ -726,7 +733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>5</v>
       </c>
@@ -737,7 +744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5</v>
       </c>
@@ -757,9 +764,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821C9B9A-57FD-DC4C-9310-B7448F7941A4}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -767,7 +774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -775,7 +782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -783,7 +790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -791,7 +798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -799,7 +806,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -807,7 +814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -815,7 +822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -823,7 +830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
@@ -831,7 +838,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
@@ -839,7 +846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -847,7 +854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -855,7 +862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3</v>
       </c>
@@ -863,7 +870,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3</v>
       </c>
@@ -871,7 +878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3</v>
       </c>
@@ -879,7 +886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3</v>
       </c>
@@ -887,7 +894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3</v>
       </c>
@@ -895,7 +902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>4</v>
       </c>
@@ -903,7 +910,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>4</v>
       </c>
@@ -911,7 +918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -919,7 +926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>4</v>
       </c>
@@ -927,7 +934,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>4</v>
       </c>
@@ -935,7 +942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>5</v>
       </c>
@@ -943,7 +950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>5</v>
       </c>
@@ -951,7 +958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>5</v>
       </c>
@@ -959,7 +966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>5</v>
       </c>
@@ -967,7 +974,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>5</v>
       </c>
@@ -975,7 +982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5</v>
       </c>
@@ -991,9 +998,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE85CEA-6988-DA4C-92A3-4FDEA2206F86}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3">
         <v>1</v>
@@ -1011,7 +1018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1029,7 +1036,7 @@
       </c>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1047,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1063,7 +1070,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1079,7 +1086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1103,9 +1110,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544395B4-F7FA-A340-9478-929130AF7087}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>4</v>
@@ -1120,7 +1127,7 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1155,7 +1162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1178,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1195,7 +1202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1218,7 +1225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1238,7 +1245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1269,13 +1276,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A8405CD-11A2-7D4B-8714-EA5300D4D8B5}">
   <dimension ref="A1:L24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="10.83203125" style="6"/>
-    <col min="14" max="14" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="6"/>
+    <col min="14" max="14" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1292,10 +1299,16 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.5</v>
+      </c>
       <c r="H2" t="s">
         <v>25</v>
       </c>
@@ -1303,10 +1316,16 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.33400000000000002</v>
+      </c>
       <c r="H3" t="s">
         <v>26</v>
       </c>
@@ -1314,12 +1333,18 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.99668874172184996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1327,22 +1352,40 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>5</v>
       </c>
@@ -1374,69 +1417,239 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" s="9">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="9">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="9">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <f>(C12+0.02)/(2+0.04)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="9"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>33</v>
       </c>
@@ -1450,38 +1663,22 @@
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1498,7 +1695,7 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>33</v>
       </c>
@@ -1514,21 +1711,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6F5FD9-3BB6-7B4A-AE4C-B18D86A2FD18}">
   <dimension ref="A3:H24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
-    <col min="2" max="2" width="13.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="10.83203125" style="6"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="10.875" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1562,33 +1759,33 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -1622,35 +1819,35 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1658,7 +1855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1678,22 +1875,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>

--- a/hwk4/test_data.xlsx
+++ b/hwk4/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yushuo Ruan\Dropbox\Spring2019\RecommenderSystems\Gitrepo\hwk4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2ED80F-AAD7-434B-A0B0-CBB1835CE44A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD85F8D9-03AD-45CD-910B-07DA45CF102C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10935" yWindow="2445" windowWidth="21180" windowHeight="16425" firstSheet="2" activeTab="4" xr2:uid="{D8D605F8-015C-0740-BF92-A813C61E88C3}"/>
+    <workbookView xWindow="10935" yWindow="2445" windowWidth="21180" windowHeight="16425" firstSheet="2" activeTab="5" xr2:uid="{D8D605F8-015C-0740-BF92-A813C61E88C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Rating Data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="35">
   <si>
     <t>User</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>P(~f|L)</t>
+  </si>
+  <si>
+    <t>like</t>
   </si>
 </sst>
 </file>
@@ -151,7 +154,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -174,12 +177,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF7E00"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -228,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -239,7 +236,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1306,7 +1302,8 @@
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="8">
+        <f>(2+0.01)/(4+0.02)</f>
         <v>0.5</v>
       </c>
       <c r="H2" t="s">
@@ -1323,8 +1320,9 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="6">
-        <v>0.33400000000000002</v>
+      <c r="G3" s="8">
+        <f>(1+0.01)/(3+0.02)</f>
+        <v>0.33443708609271522</v>
       </c>
       <c r="H3" t="s">
         <v>26</v>
@@ -1340,8 +1338,9 @@
       <c r="F4">
         <v>3</v>
       </c>
-      <c r="G4" s="10">
-        <v>0.99668874172184996</v>
+      <c r="G4" s="8">
+        <f>(3+0.01)/(3+0.02)</f>
+        <v>0.99668874172185418</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1359,7 +1358,8 @@
       <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="8">
+        <f>(2+0.01)/(4+0.02)</f>
         <v>0.5</v>
       </c>
     </row>
@@ -1370,8 +1370,9 @@
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8" s="6">
-        <v>0.66666666666666663</v>
+      <c r="G8" s="8">
+        <f>(2+0.01)/(3+0.02)</f>
+        <v>0.66556291390728473</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1381,8 +1382,9 @@
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9" s="6">
-        <v>0</v>
+      <c r="G9" s="8">
+        <f>(0+0.01)/(3+0.02)</f>
+        <v>3.3112582781456954E-3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1643,25 +1645,91 @@
       <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="8">
         <f>(C12+0.02)/(2+0.04)</f>
         <v>0.5</v>
       </c>
-      <c r="G19" s="9"/>
+      <c r="D19" s="8">
+        <f t="shared" ref="D19:L19" si="0">(D12+0.02)/(2+0.04)</f>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="J19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="8">
+        <f t="shared" si="0"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="L19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.99019607843137258</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="C20" s="8">
+        <f>(C13+0.02)/(2+0.04)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" ref="D20:L21" si="1">(D13+0.02)/(2+0.04)</f>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="1"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="8">
+        <f t="shared" si="1"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="1"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="1"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="1"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="L20" s="8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -1670,13 +1738,91 @@
       <c r="B21" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="9"/>
+      <c r="C21" s="8">
+        <f>(C14+0.02)/(1+0.04)</f>
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="D21" s="8">
+        <f t="shared" ref="D21:L21" si="2">(D14+0.02)/(1+0.04)</f>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="2"/>
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="2"/>
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="2"/>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="2"/>
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="2"/>
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="2"/>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="2"/>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="2"/>
+        <v>0.98076923076923073</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="9"/>
+      <c r="C22" s="8">
+        <f>(C15+0.02)/(2+0.04)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" ref="D22:L22" si="3">(D15+0.02)/(2+0.04)</f>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="E22" s="8">
+        <f t="shared" si="3"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="F22" s="8">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="3"/>
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="3"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="J22" s="8">
+        <f t="shared" si="3"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="3"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="L22" s="8">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1685,29 +1831,91 @@
       <c r="B23" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
+      <c r="C23" s="8">
+        <f>(C16+0.02)/(3+0.04)</f>
+        <v>0.99342105263157898</v>
+      </c>
+      <c r="D23" s="8">
+        <f t="shared" ref="D23:L23" si="4">(D16+0.02)/(3+0.04)</f>
+        <v>0.66447368421052633</v>
+      </c>
+      <c r="E23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.66447368421052633</v>
+      </c>
+      <c r="F23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.66447368421052633</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.33552631578947367</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.66447368421052633</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.66447368421052633</v>
+      </c>
+      <c r="J23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.33552631578947367</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.33552631578947367</v>
+      </c>
+      <c r="L23" s="8">
+        <f t="shared" si="4"/>
+        <v>0.66447368421052633</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="C24" s="8">
+        <f>(C17+0.02)/(0+0.04)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="8">
+        <f t="shared" ref="D24:L24" si="5">(D17+0.02)/(0+0.04)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="8">
+        <f>(F17+0.02)/(0+0.04)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="K24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1717,7 +1925,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6F5FD9-3BB6-7B4A-AE4C-B18D86A2FD18}">
-  <dimension ref="A3:H24"/>
+  <dimension ref="A3:H25"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.125" customWidth="1"/>
@@ -1763,26 +1971,80 @@
       <c r="A5" t="s">
         <v>28</v>
       </c>
+      <c r="B5" s="8">
+        <f>(1+0.01)/(3+0.02)</f>
+        <v>0.33443708609271522</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1.9230769230769232E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
+      <c r="B6" s="8">
+        <f>(2+0.01)/(3+0.02)</f>
+        <v>0.66556291390728473</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="G6" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="H6" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
+      <c r="B7" s="7">
+        <f>PRODUCT(B5:H5)/PRODUCT(B6:H6)</f>
+        <v>14.452902983343396</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="8">
+        <f>LN(B7)</f>
+        <v>2.6708952928823129</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1823,28 +2085,81 @@
       <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="B13" s="8">
+        <f>(2+0.01)/(4+0.02)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="B14" s="8">
+        <f>(2+0.01)/(4+0.02)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="G14" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="H14" s="8">
+        <v>9.8039215686274508E-3</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>30</v>
       </c>
+      <c r="B15" s="7">
+        <f>PRODUCT(B13:H13)/PRODUCT(B14:H14)</f>
+        <v>51</v>
+      </c>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
+      <c r="B16" s="7">
+        <f>LN(B15)</f>
+        <v>3.9318256327243257</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1879,20 +2194,68 @@
       <c r="A21" t="s">
         <v>28</v>
       </c>
+      <c r="B21" s="8">
+        <f>(3+0.01)/(3+0.02)</f>
+        <v>0.99668874172185418</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.66447368421052633</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.66447368421052633</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.33552631578947367</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.66447368421052633</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
+      <c r="B22" s="8">
+        <f>(0+0.01)/(3+0.02)</f>
+        <v>3.3112582781456954E-3</v>
+      </c>
+      <c r="C22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="B23" s="7">
+        <f>PRODUCT(B21:H21)/PRODUCT(B22:H22)</f>
+        <v>474.07431250887225</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>27</v>
+      </c>
+      <c r="B24" s="7">
+        <f>LN(B23)</f>
+        <v>6.1613640868516555</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
